--- a/artfynd/A 34412-2026 artfynd.xlsx
+++ b/artfynd/A 34412-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136293919</v>
       </c>
       <c r="B2" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136293909</v>
       </c>
       <c r="B3" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136293910</v>
       </c>
       <c r="B4" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>136293911</v>
       </c>
       <c r="B5" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136293912</v>
       </c>
       <c r="B6" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136293913</v>
       </c>
       <c r="B7" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>136293914</v>
       </c>
       <c r="B8" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136293915</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>136293916</v>
       </c>
       <c r="B10" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136293917</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>136293918</v>
       </c>
       <c r="B12" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>136293920</v>
       </c>
       <c r="B13" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136293921</v>
       </c>
       <c r="B14" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
